--- a/T41_V012_Files/T41_V012_Assembled_PCBs/T41_RF_Board_AttenuatorDaughterboard_V1_031426/T41_RF_Board_AttenuatorDaughterBoard_ComponentPlacement.xlsx
+++ b/T41_V012_Files/T41_V012_Assembled_PCBs/T41_RF_Board_AttenuatorDaughterboard_V1_031426/T41_RF_Board_AttenuatorDaughterBoard_ComponentPlacement.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dad\Documents\GitHub\T41\T41_V012_Files\T41_V012_Assembled_PCBs\T41_RF_Board_AttenuatorDaughterboard_V1_031426\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6353D8E4-5F95-4D15-82F2-21E59B75F17A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06208B7C-3F87-4350-BE9A-9B6BEFAFBAA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{1AEC1B75-0330-45F2-BE03-9CD656EDC538}"/>
   </bookViews>
@@ -68,12 +68,6 @@
     <t>Designator</t>
   </si>
   <si>
-    <t>Pos X</t>
-  </si>
-  <si>
-    <t>Pos Y</t>
-  </si>
-  <si>
     <t>90.551mm</t>
   </si>
   <si>
@@ -99,6 +93,12 @@
   </si>
   <si>
     <t>-66.466mm</t>
+  </si>
+  <si>
+    <t>Mid X</t>
+  </si>
+  <si>
+    <t>Mid Y</t>
   </si>
 </sst>
 </file>
@@ -502,6 +502,7 @@
   <cols>
     <col min="1" max="1" width="12.54296875" style="1" customWidth="1"/>
     <col min="2" max="2" width="13.453125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="11.7265625" customWidth="1"/>
     <col min="4" max="5" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
@@ -510,10 +511,10 @@
         <v>9</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>0</v>
@@ -527,10 +528,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>2</v>
@@ -544,10 +545,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>2</v>
@@ -561,10 +562,10 @@
         <v>5</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>2</v>
@@ -578,10 +579,10 @@
         <v>6</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>2</v>
@@ -595,10 +596,10 @@
         <v>7</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>2</v>
@@ -612,10 +613,10 @@
         <v>8</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>2</v>
